--- a/Daywise/Code and Architecture Review/Code Arch Cloud Review Guidelines.xlsx
+++ b/Daywise/Code and Architecture Review/Code Arch Cloud Review Guidelines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA4950A-BFD6-4DEA-8920-27FE606D81CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC62CBE-45B8-47B8-98F9-0CC5F05C7C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5972F415-680E-4CC7-A671-9A4E3ACFD185}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{5972F415-680E-4CC7-A671-9A4E3ACFD185}"/>
   </bookViews>
   <sheets>
     <sheet name="Code Review Guidelines" sheetId="1" r:id="rId1"/>
